--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/27.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/27.xlsx
@@ -426,13 +426,13 @@
         <v>-13.47786660041612</v>
       </c>
       <c r="E2">
-        <v>-25.05842621000172</v>
+        <v>-26.08211040180564</v>
       </c>
       <c r="F2">
-        <v>-4.282418564806737</v>
+        <v>-4.987210946824015</v>
       </c>
       <c r="G2">
-        <v>-16.3504260013875</v>
+        <v>-15.34709243232971</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.64166846041382</v>
       </c>
       <c r="E3">
-        <v>-24.63653545755112</v>
+        <v>-27.36719169875432</v>
       </c>
       <c r="F3">
-        <v>-4.125047810725095</v>
+        <v>-4.958773093885909</v>
       </c>
       <c r="G3">
-        <v>-16.07580744419133</v>
+        <v>-15.01414031824974</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.71367774513145</v>
       </c>
       <c r="E4">
-        <v>-24.67214737714744</v>
+        <v>-26.95865088767833</v>
       </c>
       <c r="F4">
-        <v>-3.945541422905845</v>
+        <v>-5.051059021129593</v>
       </c>
       <c r="G4">
-        <v>-16.15106554187875</v>
+        <v>-16.36100137847359</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.68518656039587</v>
       </c>
       <c r="E5">
-        <v>-25.39473786065536</v>
+        <v>-27.91770469844478</v>
       </c>
       <c r="F5">
-        <v>-4.026441440198051</v>
+        <v>-4.890562836837189</v>
       </c>
       <c r="G5">
-        <v>-16.27927107126016</v>
+        <v>-15.02578045173187</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.58193050441426</v>
       </c>
       <c r="E6">
-        <v>-26.14638756187051</v>
+        <v>-27.05820938873696</v>
       </c>
       <c r="F6">
-        <v>-3.906338107200956</v>
+        <v>-4.734482679169108</v>
       </c>
       <c r="G6">
-        <v>-16.17052482633704</v>
+        <v>-15.86960235650959</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.43134635165616</v>
       </c>
       <c r="E7">
-        <v>-26.27383693434239</v>
+        <v>-30.26226324575401</v>
       </c>
       <c r="F7">
-        <v>-3.974371093625476</v>
+        <v>-4.54169093494376</v>
       </c>
       <c r="G7">
-        <v>-15.98817586000324</v>
+        <v>-16.09692866736948</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.26646289353581</v>
       </c>
       <c r="E8">
-        <v>-26.99084833787287</v>
+        <v>-28.95944391611728</v>
       </c>
       <c r="F8">
-        <v>-3.757331378785381</v>
+        <v>-4.724611024829946</v>
       </c>
       <c r="G8">
-        <v>-15.96456747088304</v>
+        <v>-15.29836629217196</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.10952401829901</v>
       </c>
       <c r="E9">
-        <v>-27.48609584077372</v>
+        <v>-29.23240674387763</v>
       </c>
       <c r="F9">
-        <v>-3.600773253125885</v>
+        <v>-4.266967027642318</v>
       </c>
       <c r="G9">
-        <v>-15.13482036598456</v>
+        <v>-15.94664379811457</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.99024409817743</v>
       </c>
       <c r="E10">
-        <v>-28.46209520127687</v>
+        <v>-29.35799491353235</v>
       </c>
       <c r="F10">
-        <v>-3.418147233667693</v>
+        <v>-4.265057640778865</v>
       </c>
       <c r="G10">
-        <v>-15.00455751068538</v>
+        <v>-16.03262328724748</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.91770203551528</v>
       </c>
       <c r="E11">
-        <v>-28.31703459338917</v>
+        <v>-29.83819656154272</v>
       </c>
       <c r="F11">
-        <v>-3.776982738681994</v>
+        <v>-3.880831018133954</v>
       </c>
       <c r="G11">
-        <v>-14.82315845799304</v>
+        <v>-15.44186887646349</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.90468911302711</v>
       </c>
       <c r="E12">
-        <v>-29.1797858759085</v>
+        <v>-31.27154462597654</v>
       </c>
       <c r="F12">
-        <v>-3.549555296610792</v>
+        <v>-3.955783357474059</v>
       </c>
       <c r="G12">
-        <v>-14.86465606705534</v>
+        <v>-16.01576601148583</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.94059599081753</v>
       </c>
       <c r="E13">
-        <v>-29.55428841210584</v>
+        <v>-29.87180463139065</v>
       </c>
       <c r="F13">
-        <v>-3.422543379474349</v>
+        <v>-3.240669517617898</v>
       </c>
       <c r="G13">
-        <v>-14.41837056031214</v>
+        <v>-14.83393234898348</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.01941776406306</v>
       </c>
       <c r="E14">
-        <v>-29.4469930132051</v>
+        <v>-33.05172172194681</v>
       </c>
       <c r="F14">
-        <v>-3.222915119073697</v>
+        <v>-3.5845919242796</v>
       </c>
       <c r="G14">
-        <v>-14.02837933125356</v>
+        <v>-15.83920676059367</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.11949889054823</v>
       </c>
       <c r="E15">
-        <v>-30.98697758357153</v>
+        <v>-33.58614052501401</v>
       </c>
       <c r="F15">
-        <v>-3.107182252493772</v>
+        <v>-2.677754934147703</v>
       </c>
       <c r="G15">
-        <v>-13.03964227630297</v>
+        <v>-13.76415732456849</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.21479521399185</v>
       </c>
       <c r="E16">
-        <v>-30.40286557098116</v>
+        <v>-33.66356837359716</v>
       </c>
       <c r="F16">
-        <v>-2.873082310993021</v>
+        <v>-2.579560262219849</v>
       </c>
       <c r="G16">
-        <v>-13.27332759454506</v>
+        <v>-13.95271436209276</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.28231363238628</v>
       </c>
       <c r="E17">
-        <v>-32.22029842261254</v>
+        <v>-34.50721628851514</v>
       </c>
       <c r="F17">
-        <v>-2.551151402140841</v>
+        <v>-3.553591102597231</v>
       </c>
       <c r="G17">
-        <v>-12.88983482478496</v>
+        <v>-13.89039083979267</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.29250393168024</v>
       </c>
       <c r="E18">
-        <v>-32.41052603025275</v>
+        <v>-34.46927220480487</v>
       </c>
       <c r="F18">
-        <v>-2.774171929629148</v>
+        <v>-3.051311356277154</v>
       </c>
       <c r="G18">
-        <v>-12.82357711783509</v>
+        <v>-13.61207106467745</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.22785843088877</v>
       </c>
       <c r="E19">
-        <v>-34.11123067162541</v>
+        <v>-36.13944361018081</v>
       </c>
       <c r="F19">
-        <v>-2.321517189308581</v>
+        <v>-2.427475320535471</v>
       </c>
       <c r="G19">
-        <v>-12.26663569522118</v>
+        <v>-13.46836668526001</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.06590442354888</v>
       </c>
       <c r="E20">
-        <v>-33.51082068108143</v>
+        <v>-35.59382362665564</v>
       </c>
       <c r="F20">
-        <v>-2.266533474580361</v>
+        <v>-2.131701769161491</v>
       </c>
       <c r="G20">
-        <v>-12.12968406977308</v>
+        <v>-12.76166702945149</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.80478023406861</v>
       </c>
       <c r="E21">
-        <v>-34.08375641982088</v>
+        <v>-38.17341676767397</v>
       </c>
       <c r="F21">
-        <v>-1.978882893958233</v>
+        <v>-2.772027286423301</v>
       </c>
       <c r="G21">
-        <v>-12.65923057358718</v>
+        <v>-12.89997051818208</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.44025766491782</v>
       </c>
       <c r="E22">
-        <v>-34.77115160334119</v>
+        <v>-36.62990678029256</v>
       </c>
       <c r="F22">
-        <v>-2.020761836374164</v>
+        <v>-1.880577220798404</v>
       </c>
       <c r="G22">
-        <v>-11.60078396660618</v>
+        <v>-13.30037470385956</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.98701093578019</v>
       </c>
       <c r="E23">
-        <v>-35.43862602970177</v>
+        <v>-37.15855404323699</v>
       </c>
       <c r="F23">
-        <v>-2.067896769960859</v>
+        <v>-1.4485653961556</v>
       </c>
       <c r="G23">
-        <v>-11.88630274182283</v>
+        <v>-12.37711442512768</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.46601978536062</v>
       </c>
       <c r="E24">
-        <v>-35.79923973611757</v>
+        <v>-37.81680170380693</v>
       </c>
       <c r="F24">
-        <v>-1.78081693447926</v>
+        <v>-1.61372363219096</v>
       </c>
       <c r="G24">
-        <v>-11.86530292384238</v>
+        <v>-11.53782388732356</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.90478023743169</v>
       </c>
       <c r="E25">
-        <v>-35.8679185729179</v>
+        <v>-38.04014377762823</v>
       </c>
       <c r="F25">
-        <v>-1.794075783128469</v>
+        <v>-2.090842547018406</v>
       </c>
       <c r="G25">
-        <v>-11.75342311232999</v>
+        <v>-11.21241858283031</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.34056328786423</v>
       </c>
       <c r="E26">
-        <v>-36.33197394685392</v>
+        <v>-38.73444488401024</v>
       </c>
       <c r="F26">
-        <v>-1.628842165659454</v>
+        <v>-1.038145796234168</v>
       </c>
       <c r="G26">
-        <v>-11.43972192513928</v>
+        <v>-12.69766352171296</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.801135014411015</v>
       </c>
       <c r="E27">
-        <v>-36.1652966682906</v>
+        <v>-37.68818624927808</v>
       </c>
       <c r="F27">
-        <v>-1.609051640039171</v>
+        <v>-1.323797526313342</v>
       </c>
       <c r="G27">
-        <v>-11.55159517420855</v>
+        <v>-11.33265894687616</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.320536945519203</v>
       </c>
       <c r="E28">
-        <v>-35.99969943077812</v>
+        <v>-37.08618450012041</v>
       </c>
       <c r="F28">
-        <v>-1.661693560119677</v>
+        <v>-1.353086112574124</v>
       </c>
       <c r="G28">
-        <v>-11.67308896489011</v>
+        <v>-12.84358600690458</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.91352769936311</v>
       </c>
       <c r="E29">
-        <v>-35.7862679223226</v>
+        <v>-38.75037831980623</v>
       </c>
       <c r="F29">
-        <v>-1.721169511273279</v>
+        <v>-1.900010720068081</v>
       </c>
       <c r="G29">
-        <v>-11.39709229463898</v>
+        <v>-12.94969743091547</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.600488710560814</v>
       </c>
       <c r="E30">
-        <v>-35.64548672237215</v>
+        <v>-37.44332260273533</v>
       </c>
       <c r="F30">
-        <v>-1.815397960076528</v>
+        <v>-1.295733267073897</v>
       </c>
       <c r="G30">
-        <v>-11.34063231526561</v>
+        <v>-11.73803090199464</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.386043258523843</v>
       </c>
       <c r="E31">
-        <v>-35.80650114418887</v>
+        <v>-36.83371980995578</v>
       </c>
       <c r="F31">
-        <v>-1.693155782445405</v>
+        <v>-1.697621511113897</v>
       </c>
       <c r="G31">
-        <v>-11.85652237494931</v>
+        <v>-11.42896608086742</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.267280340104316</v>
       </c>
       <c r="E32">
-        <v>-34.84546612604407</v>
+        <v>-37.85529373287213</v>
       </c>
       <c r="F32">
-        <v>-1.75203199559938</v>
+        <v>-1.163251639976769</v>
       </c>
       <c r="G32">
-        <v>-11.68803821031494</v>
+        <v>-11.43827162521001</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.23743211057568</v>
       </c>
       <c r="E33">
-        <v>-34.88401249679735</v>
+        <v>-38.99154899579572</v>
       </c>
       <c r="F33">
-        <v>-1.501636410550756</v>
+        <v>-1.7956828158899</v>
       </c>
       <c r="G33">
-        <v>-11.11448724416712</v>
+        <v>-11.78863061966283</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.275593713505225</v>
       </c>
       <c r="E34">
-        <v>-34.46648492905314</v>
+        <v>-36.18010704253269</v>
       </c>
       <c r="F34">
-        <v>-1.724322277608333</v>
+        <v>-1.520119772409422</v>
       </c>
       <c r="G34">
-        <v>-11.78674719848771</v>
+        <v>-12.11519747658813</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.364929262614288</v>
       </c>
       <c r="E35">
-        <v>-34.19843775982812</v>
+        <v>-35.2842571434913</v>
       </c>
       <c r="F35">
-        <v>-2.011552875957242</v>
+        <v>-2.110550235898409</v>
       </c>
       <c r="G35">
-        <v>-12.27502577874868</v>
+        <v>-13.30894197335127</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.476554728675834</v>
       </c>
       <c r="E36">
-        <v>-33.79577264377709</v>
+        <v>-36.8008453528971</v>
       </c>
       <c r="F36">
-        <v>-1.944151105493655</v>
+        <v>-1.992615568761843</v>
       </c>
       <c r="G36">
-        <v>-11.64074924520022</v>
+        <v>-11.17090456766021</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.593349716504383</v>
       </c>
       <c r="E37">
-        <v>-33.52536161112006</v>
+        <v>-35.59200318010456</v>
       </c>
       <c r="F37">
-        <v>-2.01702341428533</v>
+        <v>-1.354691488600749</v>
       </c>
       <c r="G37">
-        <v>-11.68613838303202</v>
+        <v>-12.61329347175496</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.69272749636672</v>
       </c>
       <c r="E38">
-        <v>-33.0804662107105</v>
+        <v>-35.34599609387487</v>
       </c>
       <c r="F38">
-        <v>-1.846330855631867</v>
+        <v>-2.364514427718292</v>
       </c>
       <c r="G38">
-        <v>-11.94946625684214</v>
+        <v>-11.68982647606484</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.758197913453625</v>
       </c>
       <c r="E39">
-        <v>-33.22038473636249</v>
+        <v>-34.07762033754048</v>
       </c>
       <c r="F39">
-        <v>-1.641080465668414</v>
+        <v>-2.034766215685893</v>
       </c>
       <c r="G39">
-        <v>-12.17134245869179</v>
+        <v>-11.31506175565286</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.779514602210154</v>
       </c>
       <c r="E40">
-        <v>-33.20006094501607</v>
+        <v>-35.63898156946013</v>
       </c>
       <c r="F40">
-        <v>-1.819962264465953</v>
+        <v>-1.8445059622435</v>
       </c>
       <c r="G40">
-        <v>-12.33568244049658</v>
+        <v>-11.27834816762423</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.746887334610635</v>
       </c>
       <c r="E41">
-        <v>-31.82875976719835</v>
+        <v>-33.18789067112046</v>
       </c>
       <c r="F41">
-        <v>-1.647868108166953</v>
+        <v>-1.781598913307503</v>
       </c>
       <c r="G41">
-        <v>-12.50798266580458</v>
+        <v>-12.69456276733928</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.661212359831032</v>
       </c>
       <c r="E42">
-        <v>-31.53214924816995</v>
+        <v>-32.45504998669617</v>
       </c>
       <c r="F42">
-        <v>-1.65873546012428</v>
+        <v>-2.347751584955241</v>
       </c>
       <c r="G42">
-        <v>-12.08230651167626</v>
+        <v>-10.94632792046714</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.522110330442185</v>
       </c>
       <c r="E43">
-        <v>-30.78879797557386</v>
+        <v>-33.83650173900207</v>
       </c>
       <c r="F43">
-        <v>-1.825999406097556</v>
+        <v>-1.881010456950068</v>
       </c>
       <c r="G43">
-        <v>-11.8803341998062</v>
+        <v>-12.7559052043931</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.341359969640193</v>
       </c>
       <c r="E44">
-        <v>-30.99605717395691</v>
+        <v>-32.79951741903763</v>
       </c>
       <c r="F44">
-        <v>-1.860323637799956</v>
+        <v>-1.570557406831078</v>
       </c>
       <c r="G44">
-        <v>-11.36933316024607</v>
+        <v>-12.64407789242567</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.128213015296167</v>
       </c>
       <c r="E45">
-        <v>-30.11021973094648</v>
+        <v>-32.00736731053487</v>
       </c>
       <c r="F45">
-        <v>-1.924452528655083</v>
+        <v>-2.020593677791396</v>
       </c>
       <c r="G45">
-        <v>-12.26561523531619</v>
+        <v>-12.14834437678164</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.899428540758688</v>
       </c>
       <c r="E46">
-        <v>-29.53488163674596</v>
+        <v>-30.72409061047825</v>
       </c>
       <c r="F46">
-        <v>-1.679530795404159</v>
+        <v>-1.543201401721027</v>
       </c>
       <c r="G46">
-        <v>-11.89879435229963</v>
+        <v>-12.03932250924753</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.670149512205711</v>
       </c>
       <c r="E47">
-        <v>-28.98455883296382</v>
+        <v>-30.27059337369112</v>
       </c>
       <c r="F47">
-        <v>-1.702193270809947</v>
+        <v>-1.484811440232496</v>
       </c>
       <c r="G47">
-        <v>-12.42278902923515</v>
+        <v>-14.04728244865752</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.451691667722291</v>
       </c>
       <c r="E48">
-        <v>-29.14154291291372</v>
+        <v>-31.08877315078995</v>
       </c>
       <c r="F48">
-        <v>-1.539945089460622</v>
+        <v>-1.670842878083597</v>
       </c>
       <c r="G48">
-        <v>-12.32517925028479</v>
+        <v>-12.24980959106435</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.257174652355243</v>
       </c>
       <c r="E49">
-        <v>-27.95717487789564</v>
+        <v>-30.09490896032654</v>
       </c>
       <c r="F49">
-        <v>-1.72259927341051</v>
+        <v>-1.316757231756949</v>
       </c>
       <c r="G49">
-        <v>-12.19453413267394</v>
+        <v>-11.84895587803322</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.090610108078581</v>
       </c>
       <c r="E50">
-        <v>-27.73850392501325</v>
+        <v>-28.85119527343793</v>
       </c>
       <c r="F50">
-        <v>-1.69168957214245</v>
+        <v>-0.8567101407337985</v>
       </c>
       <c r="G50">
-        <v>-12.29860135565329</v>
+        <v>-11.89215644108488</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.960190707541587</v>
       </c>
       <c r="E51">
-        <v>-27.39424933095015</v>
+        <v>-28.58129369410677</v>
       </c>
       <c r="F51">
-        <v>-1.59256381525385</v>
+        <v>-2.256270002459675</v>
       </c>
       <c r="G51">
-        <v>-12.65414468017004</v>
+        <v>-13.56734801482222</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.862046702177934</v>
       </c>
       <c r="E52">
-        <v>-27.28112352176453</v>
+        <v>-28.26113963871249</v>
       </c>
       <c r="F52">
-        <v>-1.655881734421635</v>
+        <v>-1.718094611474087</v>
       </c>
       <c r="G52">
-        <v>-12.55213150188691</v>
+        <v>-12.84711660130255</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.797523623627088</v>
       </c>
       <c r="E53">
-        <v>-26.85157511976696</v>
+        <v>-28.20568394601456</v>
       </c>
       <c r="F53">
-        <v>-1.727699531509547</v>
+        <v>-1.800312561304146</v>
       </c>
       <c r="G53">
-        <v>-12.23387926039324</v>
+        <v>-12.85412857177508</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.759164428952658</v>
       </c>
       <c r="E54">
-        <v>-25.52669306476487</v>
+        <v>-29.13620837053269</v>
       </c>
       <c r="F54">
-        <v>-1.588105541891983</v>
+        <v>-1.5139881968939</v>
       </c>
       <c r="G54">
-        <v>-12.46136963233111</v>
+        <v>-12.21547816988788</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.737675631172501</v>
       </c>
       <c r="E55">
-        <v>-24.83020923391116</v>
+        <v>-27.96373210825874</v>
       </c>
       <c r="F55">
-        <v>-1.794076611495871</v>
+        <v>-2.316793010010415</v>
       </c>
       <c r="G55">
-        <v>-12.57609426293553</v>
+        <v>-13.15838968453927</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.727455742497602</v>
       </c>
       <c r="E56">
-        <v>-25.18976554164618</v>
+        <v>-28.31338464333898</v>
       </c>
       <c r="F56">
-        <v>-1.61588070090785</v>
+        <v>-1.787614517386632</v>
       </c>
       <c r="G56">
-        <v>-12.69420183296774</v>
+        <v>-13.18927582307832</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.718632885480136</v>
       </c>
       <c r="E57">
-        <v>-24.91166289588713</v>
+        <v>-26.17509808707914</v>
       </c>
       <c r="F57">
-        <v>-1.850561327957964</v>
+        <v>-1.868706715916287</v>
       </c>
       <c r="G57">
-        <v>-13.1115174345626</v>
+        <v>-13.21055126366976</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.709223934625483</v>
       </c>
       <c r="E58">
-        <v>-24.44451457420387</v>
+        <v>-26.28992660249164</v>
       </c>
       <c r="F58">
-        <v>-1.657130912465057</v>
+        <v>-2.056844692072708</v>
       </c>
       <c r="G58">
-        <v>-13.35583719187886</v>
+        <v>-13.48819510714373</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.692384364876303</v>
       </c>
       <c r="E59">
-        <v>-24.27663498579151</v>
+        <v>-25.87328887988994</v>
       </c>
       <c r="F59">
-        <v>-1.915336345387274</v>
+        <v>-2.482303302191965</v>
       </c>
       <c r="G59">
-        <v>-13.32075437096527</v>
+        <v>-14.27605577822512</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.670185973472585</v>
       </c>
       <c r="E60">
-        <v>-23.42705250568649</v>
+        <v>-24.910408508587</v>
       </c>
       <c r="F60">
-        <v>-1.889048105859432</v>
+        <v>-1.701135445636572</v>
       </c>
       <c r="G60">
-        <v>-13.14290888122181</v>
+        <v>-13.91184018512676</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.640983024015233</v>
       </c>
       <c r="E61">
-        <v>-24.03970069723619</v>
+        <v>-25.727499187687</v>
       </c>
       <c r="F61">
-        <v>-2.05847574748882</v>
+        <v>-2.19191662403839</v>
       </c>
       <c r="G61">
-        <v>-13.46021941212791</v>
+        <v>-14.54166410101906</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.60604537080336</v>
       </c>
       <c r="E62">
-        <v>-23.24242209191976</v>
+        <v>-25.27333852945774</v>
       </c>
       <c r="F62">
-        <v>-2.057370705373486</v>
+        <v>-1.156220457461807</v>
       </c>
       <c r="G62">
-        <v>-13.44345236995915</v>
+        <v>-15.15048163648779</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.568191545098978</v>
       </c>
       <c r="E63">
-        <v>-23.28614450846381</v>
+        <v>-24.55791662030395</v>
       </c>
       <c r="F63">
-        <v>-2.071666670011</v>
+        <v>-2.547913313963297</v>
       </c>
       <c r="G63">
-        <v>-13.80792061711759</v>
+        <v>-13.84304773452222</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.526510637030792</v>
       </c>
       <c r="E64">
-        <v>-22.81126608164946</v>
+        <v>-23.53525586362576</v>
       </c>
       <c r="F64">
-        <v>-2.085346329300831</v>
+        <v>-2.54943502488224</v>
       </c>
       <c r="G64">
-        <v>-14.29259149427395</v>
+        <v>-14.75799175721169</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.484557999261407</v>
       </c>
       <c r="E65">
-        <v>-22.2727942943454</v>
+        <v>-24.21572701038835</v>
       </c>
       <c r="F65">
-        <v>-2.038951127804836</v>
+        <v>-2.805808937476867</v>
       </c>
       <c r="G65">
-        <v>-13.85885173816329</v>
+        <v>-15.3797799615049</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.440372019412989</v>
       </c>
       <c r="E66">
-        <v>-22.88594514650995</v>
+        <v>-24.25191857465765</v>
       </c>
       <c r="F66">
-        <v>-2.618481933007787</v>
+        <v>-1.23174022847283</v>
       </c>
       <c r="G66">
-        <v>-13.87380098358812</v>
+        <v>-14.80811733836454</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.396410492957437</v>
       </c>
       <c r="E67">
-        <v>-22.43436118999106</v>
+        <v>-24.62544069623232</v>
       </c>
       <c r="F67">
-        <v>-2.563030190696985</v>
+        <v>-2.406840688531735</v>
       </c>
       <c r="G67">
-        <v>-13.55786856573699</v>
+        <v>-12.45864621843677</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.348291447946229</v>
       </c>
       <c r="E68">
-        <v>-21.99895294262756</v>
+        <v>-23.51704686964092</v>
       </c>
       <c r="F68">
-        <v>-2.280610750223536</v>
+        <v>-2.219039857908254</v>
       </c>
       <c r="G68">
-        <v>-13.84776120929237</v>
+        <v>-14.75076322611623</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.295660239419654</v>
       </c>
       <c r="E69">
-        <v>-21.69867888812696</v>
+        <v>-25.11298979332014</v>
       </c>
       <c r="F69">
-        <v>-2.356247321038353</v>
+        <v>-2.025808250592019</v>
       </c>
       <c r="G69">
-        <v>-13.94932650083264</v>
+        <v>-15.1493069591695</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.23283173310625</v>
       </c>
       <c r="E70">
-        <v>-22.39963232282624</v>
+        <v>-23.6297379453218</v>
       </c>
       <c r="F70">
-        <v>-2.689328883499618</v>
+        <v>-3.111714250554488</v>
       </c>
       <c r="G70">
-        <v>-14.14287099512726</v>
+        <v>-13.83624740284028</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.153242894008131</v>
       </c>
       <c r="E71">
-        <v>-22.0748411100481</v>
+        <v>-22.58798061375326</v>
       </c>
       <c r="F71">
-        <v>-2.596697527048966</v>
+        <v>-2.770921415940563</v>
       </c>
       <c r="G71">
-        <v>-13.83617029413363</v>
+        <v>-14.49968743360908</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.05209593427988</v>
       </c>
       <c r="E72">
-        <v>-21.9364509443737</v>
+        <v>-24.41429153867668</v>
       </c>
       <c r="F72">
-        <v>-2.872443639725462</v>
+        <v>-3.102895451184285</v>
       </c>
       <c r="G72">
-        <v>-13.4597830096605</v>
+        <v>-13.30850885210542</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.922317581248072</v>
       </c>
       <c r="E73">
-        <v>-22.56746209802451</v>
+        <v>-24.5949640661607</v>
       </c>
       <c r="F73">
-        <v>-2.79537647840601</v>
+        <v>-2.780605030879289</v>
       </c>
       <c r="G73">
-        <v>-13.18488554863178</v>
+        <v>-14.95428427456235</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.763276260590988</v>
       </c>
       <c r="E74">
-        <v>-22.38438947931642</v>
+        <v>-22.56707717773385</v>
       </c>
       <c r="F74">
-        <v>-2.78298410206013</v>
+        <v>-3.008997520974752</v>
       </c>
       <c r="G74">
-        <v>-13.84867995132901</v>
+        <v>-13.47929315305296</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.570528519944236</v>
       </c>
       <c r="E75">
-        <v>-22.63052109858132</v>
+        <v>-24.95010964021225</v>
       </c>
       <c r="F75">
-        <v>-2.810688021479356</v>
+        <v>-2.620622434376621</v>
       </c>
       <c r="G75">
-        <v>-13.23967866745295</v>
+        <v>-13.05590072913001</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.350070123252689</v>
       </c>
       <c r="E76">
-        <v>-23.02604707535926</v>
+        <v>-24.30817127878093</v>
       </c>
       <c r="F76">
-        <v>-2.923207650903822</v>
+        <v>-3.199331499115995</v>
       </c>
       <c r="G76">
-        <v>-13.65657099146664</v>
+        <v>-13.22727236873669</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.10250560347827</v>
       </c>
       <c r="E77">
-        <v>-22.83654855203429</v>
+        <v>-24.14788141280543</v>
       </c>
       <c r="F77">
-        <v>-2.907443819228547</v>
+        <v>-3.367985445591168</v>
       </c>
       <c r="G77">
-        <v>-12.95751658189162</v>
+        <v>-12.97763047005102</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.834186220023103</v>
       </c>
       <c r="E78">
-        <v>-23.13667316689264</v>
+        <v>-23.89328154714619</v>
       </c>
       <c r="F78">
-        <v>-2.842542061586609</v>
+        <v>-3.398548889284859</v>
       </c>
       <c r="G78">
-        <v>-12.4954319933397</v>
+        <v>-12.06100482131234</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.551501118798458</v>
       </c>
       <c r="E79">
-        <v>-23.75568386442312</v>
+        <v>-22.68640246783597</v>
       </c>
       <c r="F79">
-        <v>-3.179982493321404</v>
+        <v>-3.109655757558532</v>
       </c>
       <c r="G79">
-        <v>-12.260857464055</v>
+        <v>-12.86276474691954</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.262191549038571</v>
       </c>
       <c r="E80">
-        <v>-23.92455066016915</v>
+        <v>-24.7451554350991</v>
       </c>
       <c r="F80">
-        <v>-3.006041077714161</v>
+        <v>-3.509824310870319</v>
       </c>
       <c r="G80">
-        <v>-11.71088863725491</v>
+        <v>-12.79975216809196</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.977273713405906</v>
       </c>
       <c r="E81">
-        <v>-24.92609514254957</v>
+        <v>-26.5370409006162</v>
       </c>
       <c r="F81">
-        <v>-3.035246827234663</v>
+        <v>-3.413326963750802</v>
       </c>
       <c r="G81">
-        <v>-11.41606431769568</v>
+        <v>-12.58522918375703</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.70376427922077</v>
       </c>
       <c r="E82">
-        <v>-24.9608828798765</v>
+        <v>-25.16676089368721</v>
       </c>
       <c r="F82">
-        <v>-3.051202011779985</v>
+        <v>-3.182734329833504</v>
       </c>
       <c r="G82">
-        <v>-11.49622127917136</v>
+        <v>-11.93704355201808</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.454857137435873</v>
       </c>
       <c r="E83">
-        <v>-25.34230718859456</v>
+        <v>-27.47080771252382</v>
       </c>
       <c r="F83">
-        <v>-3.263095908313889</v>
+        <v>-3.593106712812976</v>
       </c>
       <c r="G83">
-        <v>-11.16286885606113</v>
+        <v>-10.10035681556798</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.235987699189797</v>
       </c>
       <c r="E84">
-        <v>-25.98398289853343</v>
+        <v>-27.72033115882047</v>
       </c>
       <c r="F84">
-        <v>-3.194735716765263</v>
+        <v>-3.705632969176664</v>
       </c>
       <c r="G84">
-        <v>-11.14282387355449</v>
+        <v>-10.42358995138888</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.056043674573755</v>
       </c>
       <c r="E85">
-        <v>-27.28805208699627</v>
+        <v>-27.86660539774223</v>
       </c>
       <c r="F85">
-        <v>-3.386566554803364</v>
+        <v>-3.891091176785028</v>
       </c>
       <c r="G85">
-        <v>-10.89782490337543</v>
+        <v>-10.87656915011334</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.917991898643488</v>
       </c>
       <c r="E86">
-        <v>-28.19028260591448</v>
+        <v>-29.12732803300365</v>
       </c>
       <c r="F86">
-        <v>-3.301156077002915</v>
+        <v>-3.719478301947055</v>
       </c>
       <c r="G86">
-        <v>-10.10737534848363</v>
+        <v>-10.73850190933503</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.821409876098595</v>
       </c>
       <c r="E87">
-        <v>-28.64354209781621</v>
+        <v>-29.22178747232964</v>
       </c>
       <c r="F87">
-        <v>-3.435376447278519</v>
+        <v>-4.009750665399044</v>
       </c>
       <c r="G87">
-        <v>-10.19837674721327</v>
+        <v>-11.37961650861337</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.76523992891896</v>
       </c>
       <c r="E88">
-        <v>-29.8203521097155</v>
+        <v>-31.78007640737889</v>
       </c>
       <c r="F88">
-        <v>-3.406646180647224</v>
+        <v>-3.547080134811227</v>
       </c>
       <c r="G88">
-        <v>-10.59357363427591</v>
+        <v>-10.27142002034807</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.742621952243561</v>
       </c>
       <c r="E89">
-        <v>-30.77032859433357</v>
+        <v>-31.84438753099882</v>
       </c>
       <c r="F89">
-        <v>-3.722105054981332</v>
+        <v>-3.404794779501967</v>
       </c>
       <c r="G89">
-        <v>-9.716558892202853</v>
+        <v>-11.43570570995052</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.749090075286039</v>
       </c>
       <c r="E90">
-        <v>-32.79450892678514</v>
+        <v>-33.88845239281807</v>
       </c>
       <c r="F90">
-        <v>-3.801866067094688</v>
+        <v>-3.833065696953728</v>
       </c>
       <c r="G90">
-        <v>-10.01384412793166</v>
+        <v>-10.06190746133441</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.775006350498129</v>
       </c>
       <c r="E91">
-        <v>-33.44481137970863</v>
+        <v>-34.08385151777504</v>
       </c>
       <c r="F91">
-        <v>-3.924403143521208</v>
+        <v>-4.051034011652362</v>
       </c>
       <c r="G91">
-        <v>-9.746145667004367</v>
+        <v>-10.41890764822355</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.815394342538778</v>
       </c>
       <c r="E92">
-        <v>-34.62318824361457</v>
+        <v>-35.47412247321089</v>
       </c>
       <c r="F92">
-        <v>-3.895880797108015</v>
+        <v>-4.121967112354084</v>
       </c>
       <c r="G92">
-        <v>-9.360720257745752</v>
+        <v>-10.78996458827336</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.865666257562027</v>
       </c>
       <c r="E93">
-        <v>-36.49752137115232</v>
+        <v>-37.53738806482266</v>
       </c>
       <c r="F93">
-        <v>-3.912812626821237</v>
+        <v>-3.839637135560137</v>
       </c>
       <c r="G93">
-        <v>-10.1311248301309</v>
+        <v>-10.00879104673012</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.921883480771971</v>
       </c>
       <c r="E94">
-        <v>-38.26103594701138</v>
+        <v>-37.30915071059907</v>
       </c>
       <c r="F94">
-        <v>-4.130452908028362</v>
+        <v>-4.31865218337259</v>
       </c>
       <c r="G94">
-        <v>-10.09256719558586</v>
+        <v>-10.04483526556062</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.985214441643972</v>
       </c>
       <c r="E95">
-        <v>-39.26292006494238</v>
+        <v>-39.55509494368027</v>
       </c>
       <c r="F95">
-        <v>-4.325131673197288</v>
+        <v>-4.451955550933295</v>
       </c>
       <c r="G95">
-        <v>-10.94954351759539</v>
+        <v>-10.36177829965206</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.057848911961765</v>
       </c>
       <c r="E96">
-        <v>-41.19894912236064</v>
+        <v>-43.23302643475597</v>
       </c>
       <c r="F96">
-        <v>-4.572821810308368</v>
+        <v>-5.151120833183357</v>
       </c>
       <c r="G96">
-        <v>-11.07173292724756</v>
+        <v>-11.00120635104885</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.140995017110166</v>
       </c>
       <c r="E97">
-        <v>-42.53860758804976</v>
+        <v>-43.01552609240456</v>
       </c>
       <c r="F97">
-        <v>-4.667397345053391</v>
+        <v>-4.887360368457966</v>
       </c>
       <c r="G97">
-        <v>-11.36965800118046</v>
+        <v>-10.7787231232107</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.24162186805399</v>
       </c>
       <c r="E98">
-        <v>-43.94317720016483</v>
+        <v>-44.81676285674751</v>
       </c>
       <c r="F98">
-        <v>-4.563586342134556</v>
+        <v>-4.491877061176412</v>
       </c>
       <c r="G98">
-        <v>-10.92796948584204</v>
+        <v>-10.58255857350086</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.353503424509465</v>
       </c>
       <c r="E99">
-        <v>-46.26688665314274</v>
+        <v>-46.03268982712505</v>
       </c>
       <c r="F99">
-        <v>-4.66521045511</v>
+        <v>-5.276348446934168</v>
       </c>
       <c r="G99">
-        <v>-11.4170421217204</v>
+        <v>-10.84604722716739</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.489238312991028</v>
       </c>
       <c r="E100">
-        <v>-48.2883476369527</v>
+        <v>-48.59910397666256</v>
       </c>
       <c r="F100">
-        <v>-4.871697597605833</v>
+        <v>-5.058746270627572</v>
       </c>
       <c r="G100">
-        <v>-12.42251996906728</v>
+        <v>-10.61842232514559</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.624000813858787</v>
       </c>
       <c r="E101">
-        <v>-49.94476267041185</v>
+        <v>-50.66540024950397</v>
       </c>
       <c r="F101">
-        <v>-4.932751588661767</v>
+        <v>-5.379989634535429</v>
       </c>
       <c r="G101">
-        <v>-12.16615484740631</v>
+        <v>-11.98439814156398</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.788748997180893</v>
       </c>
       <c r="E102">
-        <v>-51.75682928034414</v>
+        <v>-53.32219481540506</v>
       </c>
       <c r="F102">
-        <v>-5.07582472137109</v>
+        <v>-5.317627651350474</v>
       </c>
       <c r="G102">
-        <v>-12.56159126364279</v>
+        <v>-11.43412744238043</v>
       </c>
     </row>
   </sheetData>
